--- a/msw/test/item.xlsx
+++ b/msw/test/item.xlsx
@@ -1,58 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\eptablegenerator\table\test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ha99_main\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D947F03B-A566-4AF8-86A4-31650E3CFF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D34E295A-5031-4C1A-98E4-EC0C97A1B01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-300" windowWidth="29040" windowHeight="15840" xr2:uid="{2BE16A6F-FF36-4601-894B-FA43EFA090D5}"/>
+    <workbookView xWindow="57480" yWindow="-1740" windowWidth="29040" windowHeight="17640" xr2:uid="{2BE16A6F-FF36-4601-894B-FA43EFA090D5}"/>
   </bookViews>
   <sheets>
-    <sheet name="Item" sheetId="1" r:id="rId1"/>
+    <sheet name="CharacterWeapon" sheetId="3" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={BC8126D1-2863-47DA-A63C-83B639CFC40F}</author>
-    <author>tc={0A1FC898-4817-48C3-AF84-0A8122D9C77A}</author>
-  </authors>
-  <commentList>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{BC8126D1-2863-47DA-A63C-83B639CFC40F}">
-      <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    레코드 키값으로 사용 할지 속성 입니다</t>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="1" shapeId="0" xr:uid="{0A1FC898-4817-48C3-AF84-0A8122D9C77A}">
-      <text>
-        <t>[스레드 댓글]
-사용 중인 버전의 Excel에서 이 스레드 댓글을 읽을 수 있지만 파일을 이후 버전의 Excel에서 열면 편집 내용이 모두 제거됩니다. 자세한 정보: https://go.microsoft.com/fwlink/?linkid=870924.
-댓글:
-    레코드 컬럼 값에서 제외 하겠다는 속성 입니다</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="663" uniqueCount="180">
   <si>
     <t>Index</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,99 +46,643 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>ItemName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Category</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>design</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemDesc</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>key</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Weaepon</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Armor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Miscellaneous</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무갑옷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>책</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철로 된 검 입니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무로 된 갑옷 입니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>책 입니다</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Level</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>integer</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SellGold</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>number</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Equip</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>boolean</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_ironsword</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_woodenarmor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>item_book</t>
+    <t>표고버섯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>독버섯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하트 완드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이언 대거</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사각 강철 야삽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>철근 해머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사파이어 스태프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>페트병</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프라이팬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚜러</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>007 가방</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쇠파이프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몽둥이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>붉은 채찍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>톱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고목나무 스태프</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>자쿰의 나뭇가지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우드 완드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세계의 돼지도감</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간 벽돌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>삼각 강철 야삽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가죽 핸드백</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>막대 사탕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신문지 칼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연두색 우산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨강 우산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>하늘색 우산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노란색 우산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베이지 우산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>피코피코해머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onehandedweapon-1295</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onehandedweapon-955</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메이플 스노우보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>실버 스노우보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스카이 스노우보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골든 스노우보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>슈퍼 스노우보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>블러드 스노우보드</t>
+  </si>
+  <si>
+    <t>다크 스노우보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아쿠아 스노우보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검은색 서핑보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>황금색 서핑보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초록색 서핑보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빨간색 서핑보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지저분한 대걸레</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>흰색 대걸레</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남색 대걸레</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>노란 대걸레</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>죽창</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스틸 너클</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>냉동참치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사케</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>물고기 작살</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>강철구 망치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환목검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>빅해머</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>곡괭이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몽키 스페너</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사각 망치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 망치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>쇠 도끼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>알루미늄 야구 방망이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나무 야구 방망이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목검</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>참마도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스키 그린</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스키 스카이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스키 오렌지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스키 레드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>twohandedweapon-1020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Walk</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onehandedweapon-1017</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1029</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1079</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1120</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1159</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1173</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1227</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1279</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1310</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1411</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1416</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1426</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1453</t>
+  </si>
+  <si>
+    <t>onehandedweapon-1454</t>
+  </si>
+  <si>
+    <t>onehandedweapon-283</t>
+  </si>
+  <si>
+    <t>onehandedweapon-340</t>
+  </si>
+  <si>
+    <t>onehandedweapon-346</t>
+  </si>
+  <si>
+    <t>onehandedweapon-361</t>
+  </si>
+  <si>
+    <t>onehandedweapon-476</t>
+  </si>
+  <si>
+    <t>onehandedweapon-496</t>
+  </si>
+  <si>
+    <t>onehandedweapon-512</t>
+  </si>
+  <si>
+    <t>onehandedweapon-579</t>
+  </si>
+  <si>
+    <t>onehandedweapon-630</t>
+  </si>
+  <si>
+    <t>onehandedweapon-665</t>
+  </si>
+  <si>
+    <t>onehandedweapon-729</t>
+  </si>
+  <si>
+    <t>onehandedweapon-773</t>
+  </si>
+  <si>
+    <t>onehandedweapon-803</t>
+  </si>
+  <si>
+    <t>onehandedweapon-804</t>
+  </si>
+  <si>
+    <t>onehandedweapon-846</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1058</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1086</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1132</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1159</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1160</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1181</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1199</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1201</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1210</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1242</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1346</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1348</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1407</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1442</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1463</t>
+  </si>
+  <si>
+    <t>twohandedweapon-1555</t>
+  </si>
+  <si>
+    <t>twohandedweapon-282</t>
+  </si>
+  <si>
+    <t>twohandedweapon-477</t>
+  </si>
+  <si>
+    <t>twohandedweapon-540</t>
+  </si>
+  <si>
+    <t>twohandedweapon-546</t>
+  </si>
+  <si>
+    <t>twohandedweapon-598</t>
+  </si>
+  <si>
+    <t>twohandedweapon-617</t>
+  </si>
+  <si>
+    <t>twohandedweapon-637</t>
+  </si>
+  <si>
+    <t>twohandedweapon-651</t>
+  </si>
+  <si>
+    <t>twohandedweapon-653</t>
+  </si>
+  <si>
+    <t>twohandedweapon-666</t>
+  </si>
+  <si>
+    <t>twohandedweapon-696</t>
+  </si>
+  <si>
+    <t>twohandedweapon-709</t>
+  </si>
+  <si>
+    <t>twohandedweapon-728</t>
+  </si>
+  <si>
+    <t>twohandedweapon-748</t>
+  </si>
+  <si>
+    <t>twohandedweapon-756</t>
+  </si>
+  <si>
+    <t>twohandedweapon-776</t>
+  </si>
+  <si>
+    <t>twohandedweapon-782</t>
+  </si>
+  <si>
+    <t>twohandedweapon-793</t>
+  </si>
+  <si>
+    <t>twohandedweapon-803</t>
+  </si>
+  <si>
+    <t>twohandedweapon-851</t>
+  </si>
+  <si>
+    <t>twohandedweapon-904</t>
+  </si>
+  <si>
+    <t>twohandedweapon-920</t>
+  </si>
+  <si>
+    <t>stand1</t>
+  </si>
+  <si>
+    <t>stand1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stand2</t>
+  </si>
+  <si>
+    <t>stand2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>walk1</t>
+  </si>
+  <si>
+    <t>walk1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>walk2</t>
+  </si>
+  <si>
+    <t>서핑보드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeaponType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwingAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StabAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>none</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낚싯대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>walk2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SwingFinalAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StabFinalAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShootFinalAttack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingO1,swingO2,swingO3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoot1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shootF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabO1,stabO2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingTF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingTF,swingPF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabOF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingT2,swingP1,swingP2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingPF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabT1,stabT2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabTF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingT1,swingT2,swingT3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingOF,swingPF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swingO1,swingO2,swingO3,swingT1,swingT2,swingT3,swingP1,swingP2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabO1,stabO2,stabT1,stabT2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stabOF,stabTF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shoot1,shoot2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -162,7 +690,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -173,14 +701,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
@@ -203,12 +723,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -224,7 +738,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -262,19 +776,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color theme="0" tint="-0.34998626667073579"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -285,16 +786,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -315,9 +816,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="T G" id="{D447771D-431B-4701-BB92-C18699D59805}" userId="20e0cb65b1d67e36" providerId="Windows Live"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -635,79 +1134,93 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="A3" dT="2026-02-15T06:57:34.45" personId="{D447771D-431B-4701-BB92-C18699D59805}" id="{BC8126D1-2863-47DA-A63C-83B639CFC40F}">
-    <text>레코드 키값으로 사용 할지 속성 입니다</text>
-  </threadedComment>
-  <threadedComment ref="D3" dT="2026-02-15T06:57:57.94" personId="{D447771D-431B-4701-BB92-C18699D59805}" id="{0A1FC898-4817-48C3-AF84-0A8122D9C77A}">
-    <text>레코드 컬럼 값에서 제외 하겠다는 속성 입니다</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99B977CF-2AE1-4964-9B58-DC74286AD7EB}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92EDC631-CDBE-4E0C-A983-C4D96728F1DC}">
+  <dimension ref="A1:K73"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="4" customWidth="1"/>
-    <col min="3" max="4" width="28.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5" style="4" customWidth="1"/>
-    <col min="6" max="6" width="15.375" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="27.875" style="3" customWidth="1"/>
+    <col min="2" max="3" width="21.375" style="3" customWidth="1"/>
+    <col min="4" max="5" width="21" style="3" customWidth="1"/>
+    <col min="6" max="6" width="44.625" customWidth="1"/>
+    <col min="7" max="8" width="33.125" customWidth="1"/>
+    <col min="9" max="10" width="35.75" customWidth="1"/>
+    <col min="11" max="11" width="36.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>1</v>
@@ -716,7 +1229,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1</v>
@@ -727,80 +1240,2067 @@
       <c r="G3" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J7" s="3"/>
+      <c r="K7" s="3"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3">
-        <v>10</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="C22" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="G4" s="3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="4">
-        <v>10</v>
-      </c>
-      <c r="F5" s="4">
-        <v>19.989999999999998</v>
-      </c>
-      <c r="G5" s="4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="4">
-        <v>1</v>
-      </c>
-      <c r="F6" s="4">
-        <v>3.33</v>
-      </c>
-      <c r="G6" s="4" t="b">
-        <v>0</v>
+      <c r="C43" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A53" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A54" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A55" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A56" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A57" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A58" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A59" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A60" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A61" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A62" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A63" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E69" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>173</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>